--- a/data/trans_dic/P33B_R5-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R5-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,21</t>
+          <t>0,64; 3,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,14</t>
+          <t>1,45; 3,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,09</t>
+          <t>1,27; 2,91</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,84</t>
+          <t>2,78; 6,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 14,94</t>
+          <t>10,04; 14,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,17</t>
+          <t>7,0; 10,08</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,0</t>
+          <t>1,23; 4,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,48</t>
+          <t>5,58; 10,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,5</t>
+          <t>3,84; 6,35</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,25</t>
+          <t>4,59; 10,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,51</t>
+          <t>7,37; 11,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,32</t>
+          <t>6,7; 10,13</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,08</t>
+          <t>2,77; 7,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,32</t>
+          <t>5,63; 10,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,49</t>
+          <t>4,71; 7,86</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,72</t>
+          <t>4,15; 8,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,37; 20,25</t>
+          <t>13,55; 19,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,43</t>
+          <t>9,53; 13,1</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,33</t>
+          <t>4,38; 9,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,15; 12,21</t>
+          <t>9,49; 14,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 9,7</t>
+          <t>7,7; 10,69</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,79</t>
+          <t>11,19; 15,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,27; 25,66</t>
+          <t>19,46; 24,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,76; 19,14</t>
+          <t>16,16; 19,52</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,33</t>
+          <t>5,9; 7,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,54; 12,91</t>
+          <t>11,83; 13,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,83; 9,91</t>
+          <t>9,2; 10,42</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12247</t>
+          <t>12499</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1770; 10002</t>
+          <t>2040; 9688</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4280; 11997</t>
+          <t>4584; 12590</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7468; 18592</t>
+          <t>8090; 18491</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63799</t>
+          <t>66770</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87211</t>
+          <t>90625</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15045; 35412</t>
+          <t>14729; 35552</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52075; 76832</t>
+          <t>54815; 80312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71437; 104917</t>
+          <t>75332; 108425</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>27117</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32703</t>
+          <t>34153</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3697; 12627</t>
+          <t>3885; 12751</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18595; 33100</t>
+          <t>19884; 35681</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24820; 43270</t>
+          <t>25819; 42678</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>25300</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58614</t>
+          <t>64888</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14608; 32024</t>
+          <t>17114; 38218</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22926; 49994</t>
+          <t>31113; 49530</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40900; 73491</t>
+          <t>53300; 80555</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25253</t>
+          <t>26830</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5309; 14448</t>
+          <t>5704; 15531</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12063; 21503</t>
+          <t>12766; 22951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19159; 32846</t>
+          <t>20351; 33989</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>43803</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59314</t>
+          <t>60052</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11643; 23509</t>
+          <t>11246; 23466</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34363; 52057</t>
+          <t>35729; 52674</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48928; 70755</t>
+          <t>50932; 70012</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>72952</t>
+          <t>89722</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113562</t>
+          <t>134235</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>27806; 58169</t>
+          <t>31455; 65178</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35259; 103607</t>
+          <t>73170; 108741</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69819; 142712</t>
+          <t>114679; 159322</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>95273</t>
+          <t>106588</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>162369</t>
+          <t>181944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>257642</t>
+          <t>288531</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>42330; 137329</t>
+          <t>89287; 125060</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>145038; 183543</t>
+          <t>161621; 200681</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>160498; 314695</t>
+          <t>263204; 317919</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>427630</t>
+          <t>474236</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>646547</t>
+          <t>711812</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>168381; 253439</t>
+          <t>208439; 268293</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>348865; 472318</t>
+          <t>441591; 507802</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>557091; 705134</t>
+          <t>668340; 756581</t>
         </is>
       </c>
     </row>
